--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle Ampatacocha / Calle s / n</t>
+          <t>Calle Ampatacocha / Calle Quezada</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1099,6 +1099,162 @@
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-423736</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-16.3940759</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-71.5540359</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Urbano Victor Andrés Belaúnde / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-454422</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-16.3931199</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-71.5435637</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-449284</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-16.408531</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-71.5555226</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fernandini / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>040126</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-483273</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-16.3975637</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-415023</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-16.3971782</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-415024</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-16.3980865</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-400784</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-16.3879869</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-400785</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-16.3876891</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-83933</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-16.3933633</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-83934</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-16.3933736</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-83935</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-16.3901439</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-83936</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-16.3899759</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-83937</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-16.3904642</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-84020</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-16.3843998</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-84021</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-16.3847353</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-423736</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-16.3940759</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-454422</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-16.3931199</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>040126</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>YANAHUARA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-449284</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>040126</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>YANAHUARA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-16.408531</t>
@@ -1252,11 +1177,6 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>040126</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
+++ b/Intersecciones/excels/AREQUIPA-AREQUIPA-YANAHUARA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-483273</t>
+          <t>I-84021</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-16.3975637</t>
+          <t>-16.3847353</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-71.5572754</t>
+          <t>-71.5381963</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle Miguel Angel Buonarotti / Frai Angelico</t>
+          <t>Avenida León Velarde / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-415023</t>
+          <t>I-84020</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-16.3971782</t>
+          <t>-16.3843998</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-71.5511788</t>
+          <t>-71.5395591</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle Chullo / Calle s / n</t>
+          <t>Avenida León Velarde / Calle Tacna</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-415024</t>
+          <t>I-83937</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-16.3980865</t>
+          <t>-16.3904642</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-71.5515932</t>
+          <t>-71.5425639</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle Chullo / Pasaje Canoa</t>
+          <t>Calle Ampatacocha / Pasaje Lima</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-400784</t>
+          <t>I-83936</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-16.3879869</t>
+          <t>-16.3899759</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-71.5409421</t>
+          <t>-71.5417797</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle Cuzco / Cuesta del Ángel</t>
+          <t>Calle Ampatacocha / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-400785</t>
+          <t>I-83935</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-16.3876891</t>
+          <t>-16.3901439</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-71.5417736</t>
+          <t>-71.5422344</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cuesta del Ángel / Calle s / n</t>
+          <t>Calle Ampatacocha / Calle las Beatas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-83933</t>
+          <t>I-83934</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-16.3933633</t>
+          <t>-16.3933736</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-71.5526365</t>
+          <t>-71.5515736</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-83934</t>
+          <t>I-83933</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-16.3933736</t>
+          <t>-16.3933633</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-71.5515736</t>
+          <t>-71.5526365</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-83935</t>
+          <t>I-483273</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-16.3901439</t>
+          <t>-16.3975637</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-71.5422344</t>
+          <t>-71.5572754</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle Ampatacocha / Calle las Beatas</t>
+          <t>Calle Miguel Angel Buonarotti / Frai Angelico</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-83936</t>
+          <t>I-454422</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-16.3899759</t>
+          <t>-16.3931199</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-71.5417797</t>
+          <t>-71.5435637</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle Ampatacocha / Calle Quezada</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-83937</t>
+          <t>I-449284</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-16.3904642</t>
+          <t>-16.408531</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-71.5425639</t>
+          <t>-71.5555226</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle Ampatacocha / Pasaje Lima</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-84020</t>
+          <t>I-423736</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-16.3843998</t>
+          <t>-16.3940759</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-71.5395591</t>
+          <t>-71.5540359</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida León Velarde / Calle Tacna</t>
+          <t>Urbano Victor Andrés Belaúnde / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-84021</t>
+          <t>I-415024</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-16.3847353</t>
+          <t>-16.3980865</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-71.5381963</t>
+          <t>-71.5515932</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida León Velarde / Calle s / n</t>
+          <t>Calle Chullo / Pasaje Canoa</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-423736</t>
+          <t>I-415023</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-16.3940759</t>
+          <t>-16.3971782</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-71.5540359</t>
+          <t>-71.5511788</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Urbano Victor Andrés Belaúnde / Calle s / n</t>
+          <t>Calle Chullo / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-454422</t>
+          <t>I-400785</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-16.3931199</t>
+          <t>-16.3876891</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-71.5435637</t>
+          <t>-71.5417736</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Cuesta del Ángel / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-449284</t>
+          <t>I-400784</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-16.408531</t>
+          <t>-16.3879869</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-71.5555226</t>
+          <t>-71.5409421</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fernandini / Calle s / n</t>
+          <t>Calle Cuzco / Cuesta del Ángel</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
